--- a/output/2026-09-14_00_Croazia_Primorsko-goranska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-14_00_Croazia_Primorsko-goranska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore esclusivo macchine per lavorazione metalli (marchio Durma: presse CNC, cesoie, laser, plasma) per Croazia/BiH/Slovenia. Fondata 1992; verificata su fininfo.hr, tvrtke.hr e sito ufficiale</t>
+          <t>Distributore esclusivo macchine per lavorazione metalli (marchio Durma: presse CNC, cesoie, laser, plasma) per Croazia/BiH/Slovenia. Fondata 1992; verificata su fininfo.hr, tvrtke.hr e sito ufficiale [DUPLICATO — vedi anche: 2026-09-14_00_Croazia_Primorsko-goranska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,10 +536,9 @@
           <t>+385 51 684 359</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Produttore e distributore di attrezzature per taglio ossiacetilenico/plasma e saldatura, abrasivi, DPI industriali. Storica (1962), ISO 9001</t>
+          <t>Produttore e distributore di attrezzature per taglio ossiacetilenico/plasma e saldatura, abrasivi, DPI industriali. Storica (1962), ISO 9001 [DUPLICATO — vedi anche: 2026-09-14_00_Croazia_Primorsko-goranska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -581,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Distributore autorizzato SKF/FAG/NTN, cuscinetti, componenti e utensili per manutenzione industriale. Distributore SKF dal 1990</t>
+          <t>Distributore autorizzato SKF/FAG/NTN, cuscinetti, componenti e utensili per manutenzione industriale. Distributore SKF dal 1990 [DUPLICATO — vedi anche: 2026-09-14_00_Croazia_Primorsko-goranska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -616,10 +615,9 @@
           <t>051 223 633</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distribuzione cinghie industriali, gomma, plastica, cuscinetti, guarnizioni e utensili. Fondata 1994</t>
+          <t>Distribuzione cinghie industriali, gomma, plastica, cuscinetti, guarnizioni e utensili. Fondata 1994 [DUPLICATO — vedi anche: 2026-09-08_19_Croazia_Sisacko-moslavacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -696,7 +694,6 @@
           <t>051 275453 / 091 5183461</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Rivenditore autorizzato Makita/REMS, vendita utensili elettrici/manuali e macchine utensili (noleggio/assistenza accessorio)</t>
@@ -734,7 +731,6 @@
           <t>051 371 069</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Rivenditore di utensili professionali</t>
@@ -863,7 +859,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ferramenta, utensili manuali/elettrici (Bosch, Makita), materiale idraulico ed elettrico. Attività 30 anni</t>
+          <t>Ferramenta, utensili manuali/elettrici (Bosch, Makita), materiale idraulico ed elettrico. Attività 30 anni [DUPLICATO — vedi anche: 2026-09-14_00_Croazia_Primorsko-goranska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/output/2026-09-14_00_Croazia_Primorsko-goranska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-14_00_Croazia_Primorsko-goranska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-14_00_Croazia_Primorsko-goranska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-14_00_Croazia_Primorsko-goranska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Grossista utensili industriali, fissaggi, attrezzature officina</t>
+          <t>Grossista utensili industriali, fissaggi, attrezzature officina [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Grossista utensili industriali, fissaggi, attrezzature officina. Sede distinta da Viškovo</t>
+          <t>Grossista utensili industriali, fissaggi, attrezzature officina. Sede distinta da Viškovo [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
